--- a/tests/fixtures/_downloaded.xlsx
+++ b/tests/fixtures/_downloaded.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Πελατες Ημερας" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Πρακτορεια Ημερας" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Πελάτες Ημέρας" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Πρακτορεία Ημέρας" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Μόνο Πρακτορεία" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Πελάτες ανά Περιοχή" state="visible" r:id="rId7"/>
   </sheets>
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>15/05/26</t>
+    <t>15/06/26</t>
   </si>
   <si>
     <t>ID_Παραγγελίας</t>
@@ -157,7 +157,7 @@
     <t>2674728848</t>
   </si>
   <si>
-    <t>ΜΑΚΕΔΟΝΙΑ</t>
+    <t>ΜΑΚΕΔΟΝΙΑ ΘΕΣΣΑΛΟΝΙΚΗ ΠΕΡΙΟΧΗ ΤΕΣΤ ΜΑΚΡΥ</t>
   </si>
   <si>
     <t>ΜΕΤΑΦ Α</t>
@@ -175,7 +175,7 @@
     <t>ΘΕΣΣΑΛΙΑ</t>
   </si>
   <si>
-    <t>ΜΕΤΑΦ Β</t>
+    <t>ΜΕΤΑΦΟΡΙΚΗ ΑΦΟΙ ΠΑΠΑΣ</t>
   </si>
   <si>
     <t>ΟΔΟΣ 2</t>
@@ -239,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -262,6 +262,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
     <font>
@@ -549,16 +557,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="thick">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thick">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thick">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -642,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -701,14 +709,32 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -730,11 +756,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -751,11 +780,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -772,11 +804,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -786,16 +821,16 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1180,7 +1215,7 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="7" max="13" width="4.59" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1571,12 +1606,11 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="7" max="13" width="4.59" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="14" max="15" width="21.7109375" customWidth="1"/>
+    <col min="16" max="16" width="41.7109375" customWidth="1"/>
+    <col min="17" max="18" width="27.7109375" customWidth="1"/>
     <col min="19" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1704,20 +1738,20 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" ht="33" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="22" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1741,45 +1775,45 @@
       <c r="L3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="N3" s="12" t="s">
+      <c r="M3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="25" t="s">
         <v>0</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="T3" s="23" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T3" s="26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="33" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="27" t="s">
         <v>0</v>
       </c>
       <c r="F4" s="19" t="s">
@@ -1803,28 +1837,28 @@
       <c r="L4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19" t="s">
+      <c r="M4" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="Q4" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="19" t="s">
+      <c r="R4" s="30" t="s">
         <v>0</v>
       </c>
       <c r="S4" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="T4" s="25" t="s">
+      <c r="T4" s="31" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1835,13 +1869,13 @@
       <c r="B5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="27" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="19" t="s">
@@ -1865,28 +1899,28 @@
       <c r="L5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M5" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="R5" s="19" t="s">
+      <c r="M5" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="P5" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5" s="30" t="s">
         <v>0</v>
       </c>
       <c r="S5" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="T5" s="25" t="s">
+      <c r="T5" s="31" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1897,13 +1931,13 @@
       <c r="B6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="22" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1927,28 +1961,28 @@
       <c r="L6" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="M6" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12" t="s">
+      <c r="M6" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" s="25" t="s">
         <v>0</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="T6" s="23" t="s">
+      <c r="T6" s="26" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1959,13 +1993,13 @@
       <c r="B7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="27" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="19" t="s">
@@ -1989,28 +2023,28 @@
       <c r="L7" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M7" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="O7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="P7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="R7" s="19" t="s">
+      <c r="M7" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="R7" s="30" t="s">
         <v>0</v>
       </c>
       <c r="S7" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="T7" s="25" t="s">
+      <c r="T7" s="31" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2021,13 +2055,13 @@
       <c r="B8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="22" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -2051,28 +2085,28 @@
       <c r="L8" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="M8" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R8" s="12" t="s">
+      <c r="M8" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" s="25" t="s">
         <v>0</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="T8" s="23" t="s">
+      <c r="T8" s="26" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2083,13 +2117,13 @@
       <c r="B9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="27" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="19" t="s">
@@ -2113,33 +2147,33 @@
       <c r="L9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="M9" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N9" s="19" t="s">
+      <c r="M9" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="P9" s="19" t="s">
+      <c r="P9" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="Q9" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="R9" s="19" t="s">
+      <c r="R9" s="30" t="s">
         <v>0</v>
       </c>
       <c r="S9" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="T9" s="25" t="s">
+      <c r="T9" s="31" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.39370078740157477" right="0.39370078740157477" top="0.39370078740157477" bottom="0.39370078740157477" header="0.3" footer="0.3"/>
+  <pageMargins left="0.11811023622047244" right="0.11811023622047244" top="0.39370078740157477" bottom="0.39370078740157477" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
@@ -2156,12 +2190,11 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="7" max="13" width="4.59" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="14" max="15" width="21.7109375" customWidth="1"/>
+    <col min="16" max="16" width="41.7109375" customWidth="1"/>
+    <col min="17" max="18" width="27.7109375" customWidth="1"/>
     <col min="19" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2228,250 +2261,250 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="28" t="s">
+      <c r="Q2" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="28" t="s">
+      <c r="R2" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="28" t="s">
+      <c r="S2" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="T2" s="29" t="s">
+      <c r="T2" s="35" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="32" t="s">
+      <c r="D3" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="N3" s="32" t="s">
+      <c r="G3" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="32" t="s">
+      <c r="O3" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="P3" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="S3" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="T3" s="36" t="s">
+      <c r="R3" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="S3" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3" s="43" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="39" t="s">
+      <c r="D4" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="I4" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="L4" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="M4" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" s="39" t="s">
+      <c r="G4" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="M4" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="39" t="s">
+      <c r="O4" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="39" t="s">
+      <c r="P4" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="S4" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="T4" s="43" t="s">
+      <c r="R4" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="T4" s="51" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="46" t="s">
+      <c r="E5" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="I5" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="M5" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="N5" s="46" t="s">
+      <c r="G5" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="K5" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="M5" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="O5" s="46" t="s">
+      <c r="O5" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="P5" s="46" t="s">
+      <c r="P5" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="Q5" s="46" t="s">
+      <c r="Q5" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="R5" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="S5" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="T5" s="50" t="s">
+      <c r="R5" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="S5" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="T5" s="59" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2532,52 +2565,52 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="63" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="55">
+      <c r="A5" s="64">
         <v>3061071244</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" s="67" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="55">
+      <c r="A6" s="64">
         <v>720416398</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="68" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="17" t="s">
@@ -2586,7 +2619,7 @@
       <c r="D6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="69" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2611,52 +2644,52 @@
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="63" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="55">
+      <c r="A10" s="64">
         <v>334074002</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="72" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="55">
+      <c r="A11" s="64">
         <v>2288386452</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="73" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -2665,15 +2698,15 @@
       <c r="D11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="74" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="55">
+      <c r="A12" s="64">
         <v>6197011352</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="73" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
@@ -2682,15 +2715,15 @@
       <c r="D12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="74" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="55">
+      <c r="A13" s="64">
         <v>2674728848</v>
       </c>
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="73" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -2699,15 +2732,15 @@
       <c r="D13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="74" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="55">
+      <c r="A14" s="64">
         <v>52268394</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="68" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="17" t="s">
@@ -2716,12 +2749,11 @@
       <c r="D14" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="69" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:E6"/>
   <mergeCells count="2">
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:E8"/>
